--- a/inst/extdata/a3_2025_messy.xlsx
+++ b/inst/extdata/a3_2025_messy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ernestcaballero/Developer/data501/peridial/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DFCAD6-E13C-AE4A-8698-9265DC31506B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89267B1-AF4A-4C4D-BDDC-5B2D456C23FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="24240" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2067,7 +2067,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>76</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>82</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>83</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>86</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>87</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -2686,8 +2686,11 @@
       <c r="Q47" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>45981</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>89</v>
       </c>
@@ -2736,6 +2739,7 @@
       <c r="Q48" t="s">
         <v>111</v>
       </c>
+      <c r="S48" s="3"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
